--- a/backend/tests/fixtures/phd/فرص_الدكتوراه_والتقديمات.xlsx
+++ b/backend/tests/fixtures/phd/فرص_الدكتوراه_والتقديمات.xlsx
@@ -7,11 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ملخص" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفرص" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المواعيد القادمة" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المراجع والوثائق" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خطة 30 يوماً" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفرص" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,55 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ملخص فرص الدكتوراه والتقديمات – عبد الله بن عيشة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>التاريخ اليوم:</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>إجمالي الفرص المسجلة:</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>COUNTA(الفرص!C2:C131)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
           <t>#</t>
         </is>
       </c>
@@ -476,429 +429,107 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>المؤسسة / المجموعة</t>
+          <t>المؤسسة / الجامعة</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>المشرف / البرنامج</t>
+          <t>البرنامج / التخصص</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>النوع</t>
+          <t>المجال الدقيق</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>التمويل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>الموعد النهائي</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظة الموعد</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>الأيام المتبقية</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>حالة الموعد</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>الإجراء التالي</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>الرابط / الاتصال</t>
-        </is>
-      </c>
       <c r="M1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>المشرف / جهة الاتصال</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>التحقق</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>401</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ألمانيا</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ruhr-Universität Bochum – CASA (Görtz Institute)</t>
+          <t>ANU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+1234567890</t>
+          <t>PhD Cybernetics</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>وظيفة دكتوراه معلنة</t>
+          <t>Critical Infrastructure</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Full RTP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>مفتوح/مستمر (راقب البوابة)</t>
-        </is>
-      </c>
-      <c r="H2">
-        <f>IF(F2="","",F2-TODAY())</f>
-        <v/>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>لم يُتواصل بعد</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>افتح بوابة الوظائف وقدّم مباشرة على منصب Vulnerabi</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>casa.rub.de/en/jobs/doctoral-and-postdoctoral-posi</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>موضوع قريب جداً من SecuraX؛ تمويل DFG €53M (2026-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ألمانيا</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CISPA – SprintML</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Boenisch / Dziedzic</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>وظيفة دكتوراه معلنة</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>قبول مستمر (rolling)</t>
-        </is>
-      </c>
-      <c r="H3">
-        <f>IF(F3="","",F3-TODAY())</f>
-        <v/>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>لم يُتواصل بعد</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>قدّم الآن (الخطوة التالية المسجلة)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>لا موعد نهائي ثابت؛ آخر تحقق من الصلاحية 15.08.202</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الأيام المتبقية</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الفرصة / الحدث</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الإجراء المطلوب</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ملاحظة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الرابط / الاتصال</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>IF(A2="","",A2-TODAY())</f>
-        <v/>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>بدء نافذة مقابلات HPI (19–30.10)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>تحضير إنجليزي شفهي + عبارة التأجيل</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>إن وصلتك دعوة</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>IF(A3="","",A3-TODAY())</f>
-        <v/>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>نهاية نافذة مقابلات HPI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>الاسم</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>البريد</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المجال / الدور</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lalia Saoudi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>researcher1@example.edu</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Réseaux &amp; Sécurité – رسالة مخصصة لـ CISPA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>تسمح بمشاركتها مع أي مؤسسة</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Noureddine Amraoui</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>researcher2@example.edu</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Web Security – رسالة عامة 02.08.2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المهمة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الأولوية</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>التفاصيل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>المدة التقريبية</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>متابعة إيطاليا: رد IMT Lucca على إيميل 31.08</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ابحث عن رد في البريد؛ إن لم يوجد أعد المراسلة وأرف</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>15 دقيقة</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>التقديم المباشر: CASA Bochum + CISPA SprintML</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>بلا موعد ثابت؛ استخدم الملفات الجاهزة</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ساعة لكل واحد</t>
+          <t>2027-07-01</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Prof. Gene Spafford</t>
         </is>
       </c>
     </row>

--- a/backend/tests/fixtures/phd/فرص_الدكتوراه_والتقديمات.xlsx
+++ b/backend/tests/fixtures/phd/فرص_الدكتوراه_والتقديمات.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفرص" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="الفرص" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,17 +499,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ANU</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PhD Cybernetics</t>
+          <t>PhD Information Security</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
